--- a/ExcelSheets/spacecraft_values.xlsx
+++ b/ExcelSheets/spacecraft_values.xlsx
@@ -7,15 +7,16 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary (check view)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Constants" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method &amp; Definitions" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mission success" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary (check view)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Constants" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method &amp; Definitions" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="g0">Constants!$B$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary (check view)'!$A$4:$L$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Data'!$A$1:$AW$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Summary (check view)'!$A$4:$L$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Data'!$A$1:$AW$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -23,11 +24,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="#,##0.0#####"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0"/>
-    <numFmt numFmtId="166" formatCode="0.000E+00"/>
-    <numFmt numFmtId="167" formatCode="0.0000"/>
+  <numFmts count="5">
+    <numFmt numFmtId="164" formatCode="0.000E+00"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0#####"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0"/>
+    <numFmt numFmtId="168" formatCode="0.000000000"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -139,7 +141,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -152,10 +154,10 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -167,10 +169,10 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -182,10 +184,10 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -197,10 +199,10 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -212,10 +214,10 @@
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -232,28 +234,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -267,6 +269,65 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -633,6 +694,680 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="48" t="inlineStr">
+        <is>
+          <t>Spacecraft</t>
+        </is>
+      </c>
+      <c r="B1" s="48" t="inlineStr">
+        <is>
+          <t>TVC engines, N</t>
+        </is>
+      </c>
+      <c r="C1" s="48" t="inlineStr">
+        <is>
+          <t>TVC failure rate, each</t>
+        </is>
+      </c>
+      <c r="D1" s="48" t="inlineStr">
+        <is>
+          <t>RCS thrusters, N</t>
+        </is>
+      </c>
+      <c r="E1" s="48" t="inlineStr">
+        <is>
+          <t>RCS failure rate, each</t>
+        </is>
+      </c>
+      <c r="F1" s="48" t="inlineStr">
+        <is>
+          <t>Max RCS failures tolerated</t>
+        </is>
+      </c>
+      <c r="G1" s="48" t="inlineStr">
+        <is>
+          <t>Max TVC failures tolerated</t>
+        </is>
+      </c>
+      <c r="H1" s="48" t="inlineStr">
+        <is>
+          <t>TVC ensemble success</t>
+        </is>
+      </c>
+      <c r="I1" s="48" t="inlineStr">
+        <is>
+          <t>RCS ensemble success</t>
+        </is>
+      </c>
+      <c r="J1" s="48" t="inlineStr">
+        <is>
+          <t>Mission success</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ariane 5 ECA</t>
+        </is>
+      </c>
+      <c r="B2" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D2" s="49" t="n"/>
+      <c r="E2" s="50" t="n"/>
+      <c r="F2" s="49" t="n"/>
+      <c r="G2" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="50" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I2" s="50" t="n"/>
+      <c r="J2" s="50" t="n">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Delta IV Heavy</t>
+        </is>
+      </c>
+      <c r="B3" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" s="50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D3" s="49" t="n"/>
+      <c r="E3" s="50" t="n"/>
+      <c r="F3" s="49" t="n"/>
+      <c r="G3" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="50" t="n">
+        <v>0.970299</v>
+      </c>
+      <c r="I3" s="50" t="n"/>
+      <c r="J3" s="50" t="n">
+        <v>0.970299</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Vega</t>
+        </is>
+      </c>
+      <c r="B4" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="50" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D4" s="49" t="n"/>
+      <c r="E4" s="50" t="n"/>
+      <c r="F4" s="49" t="n"/>
+      <c r="G4" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="50" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="I4" s="50" t="n"/>
+      <c r="J4" s="50" t="n">
+        <v>0.985</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Vega-C</t>
+        </is>
+      </c>
+      <c r="B5" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="50" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D5" s="49" t="n"/>
+      <c r="E5" s="50" t="n"/>
+      <c r="F5" s="49" t="n"/>
+      <c r="G5" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="50" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="I5" s="50" t="n"/>
+      <c r="J5" s="50" t="n">
+        <v>0.985</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Apollo Command &amp; Service Module</t>
+        </is>
+      </c>
+      <c r="B6" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D6" s="49" t="n">
+        <v>16</v>
+      </c>
+      <c r="E6" s="50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F6" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="50" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I6" s="50" t="n">
+        <v>0.9995997710803205</v>
+      </c>
+      <c r="J6" s="50" t="n">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Apollo Lunar Module</t>
+        </is>
+      </c>
+      <c r="B7" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D7" s="49" t="n">
+        <v>16</v>
+      </c>
+      <c r="E7" s="50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F7" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="50" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I7" s="50" t="n">
+        <v>0.9995997710803205</v>
+      </c>
+      <c r="J7" s="50" t="n">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Crew Dragon (Dragon 2)</t>
+        </is>
+      </c>
+      <c r="B8" s="49" t="n"/>
+      <c r="C8" s="50" t="n"/>
+      <c r="D8" s="49" t="n">
+        <v>16</v>
+      </c>
+      <c r="E8" s="50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F8" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="49" t="n"/>
+      <c r="H8" s="50" t="n"/>
+      <c r="I8" s="50" t="n">
+        <v>0.9984207285155099</v>
+      </c>
+      <c r="J8" s="50" t="n">
+        <v>0.9984207285155099</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Orion (CM + European Service Module)</t>
+        </is>
+      </c>
+      <c r="B9" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D9" s="49" t="n">
+        <v>24</v>
+      </c>
+      <c r="E9" s="50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F9" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="50" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I9" s="50" t="n">
+        <v>0.9999963240750266</v>
+      </c>
+      <c r="J9" s="50" t="n">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Cassini (Cassini-Huygens)</t>
+        </is>
+      </c>
+      <c r="B10" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D10" s="49" t="n">
+        <v>16</v>
+      </c>
+      <c r="E10" s="50" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F10" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="50" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="I10" s="50" t="n">
+        <v>0.9999999840198219</v>
+      </c>
+      <c r="J10" s="50" t="n">
+        <v>0.9999</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Europa Clipper</t>
+        </is>
+      </c>
+      <c r="B11" s="49" t="n"/>
+      <c r="C11" s="50" t="n"/>
+      <c r="D11" s="49" t="n">
+        <v>24</v>
+      </c>
+      <c r="E11" s="50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F11" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" s="49" t="n"/>
+      <c r="H11" s="50" t="n"/>
+      <c r="I11" s="50" t="n">
+        <v>0.9999094623582535</v>
+      </c>
+      <c r="J11" s="50" t="n">
+        <v>0.9999094623582535</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Juno</t>
+        </is>
+      </c>
+      <c r="B12" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D12" s="49" t="n">
+        <v>12</v>
+      </c>
+      <c r="E12" s="50" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F12" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="50" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I12" s="50" t="n">
+        <v>0.9999734134184508</v>
+      </c>
+      <c r="J12" s="50" t="n">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>New Horizons</t>
+        </is>
+      </c>
+      <c r="B13" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" s="50" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="D13" s="49" t="n">
+        <v>12</v>
+      </c>
+      <c r="E13" s="50" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F13" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" s="50" t="n">
+        <v>0.9999999993749999</v>
+      </c>
+      <c r="I13" s="50" t="n">
+        <v>0.9998500087944048</v>
+      </c>
+      <c r="J13" s="50" t="n">
+        <v>0.9998500087944048</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Voyager 1</t>
+        </is>
+      </c>
+      <c r="B14" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="C14" s="50" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="D14" s="49" t="n">
+        <v>16</v>
+      </c>
+      <c r="E14" s="50" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F14" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" s="50" t="n">
+        <v>0.9999999993749999</v>
+      </c>
+      <c r="I14" s="50" t="n">
+        <v>0.9999999840198219</v>
+      </c>
+      <c r="J14" s="50" t="n">
+        <v>0.9999999840198219</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>GOES-16 (GOES-R)</t>
+        </is>
+      </c>
+      <c r="B15" s="49" t="n"/>
+      <c r="C15" s="50" t="n"/>
+      <c r="D15" s="49" t="n"/>
+      <c r="E15" s="50" t="n"/>
+      <c r="F15" s="49" t="n"/>
+      <c r="G15" s="49" t="n"/>
+      <c r="H15" s="50" t="n"/>
+      <c r="I15" s="50" t="n"/>
+      <c r="J15" s="50" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>GOES-19 (GOES-U)</t>
+        </is>
+      </c>
+      <c r="B16" s="49" t="n"/>
+      <c r="C16" s="50" t="n"/>
+      <c r="D16" s="49" t="n"/>
+      <c r="E16" s="50" t="n"/>
+      <c r="F16" s="49" t="n"/>
+      <c r="G16" s="49" t="n"/>
+      <c r="H16" s="50" t="n"/>
+      <c r="I16" s="50" t="n"/>
+      <c r="J16" s="50" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Meteosat Second Generation (MSG)</t>
+        </is>
+      </c>
+      <c r="B17" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" s="50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D17" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" s="50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F17" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="50" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="I17" s="50" t="n">
+        <v>0.979903989801</v>
+      </c>
+      <c r="J17" s="50" t="n">
+        <v>0.979903989801</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Solar Dynamics Observatory (SDO)</t>
+        </is>
+      </c>
+      <c r="B18" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D18" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="E18" s="50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F18" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="50" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I18" s="50" t="n">
+        <v>0.9993070590010299</v>
+      </c>
+      <c r="J18" s="50" t="n">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>GRACE-FO (per satellite)</t>
+        </is>
+      </c>
+      <c r="B19" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" s="50" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="D19" s="49" t="n">
+        <v>12</v>
+      </c>
+      <c r="E19" s="50" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="F19" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="50" t="n">
+        <v>0.9999910000000001</v>
+      </c>
+      <c r="I19" s="50" t="n">
+        <v>0.9999460011692546</v>
+      </c>
+      <c r="J19" s="50" t="n">
+        <v>0.9999460011692546</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SMAP</t>
+        </is>
+      </c>
+      <c r="B20" s="49" t="n"/>
+      <c r="C20" s="50" t="n"/>
+      <c r="D20" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="E20" s="50" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F20" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="49" t="n"/>
+      <c r="H20" s="50" t="n"/>
+      <c r="I20" s="50" t="n">
+        <v>0.9998258787187658</v>
+      </c>
+      <c r="J20" s="50" t="n">
+        <v>0.9998258787187658</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Sentinel-1A</t>
+        </is>
+      </c>
+      <c r="B21" s="49" t="n"/>
+      <c r="C21" s="50" t="n"/>
+      <c r="D21" s="49" t="n"/>
+      <c r="E21" s="50" t="n"/>
+      <c r="F21" s="49" t="n"/>
+      <c r="G21" s="49" t="n"/>
+      <c r="H21" s="50" t="n"/>
+      <c r="I21" s="50" t="n"/>
+      <c r="J21" s="50" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Sentinel-3A</t>
+        </is>
+      </c>
+      <c r="B22" s="49" t="n"/>
+      <c r="C22" s="50" t="n"/>
+      <c r="D22" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="E22" s="50" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F22" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="49" t="n"/>
+      <c r="H22" s="50" t="n"/>
+      <c r="I22" s="50" t="n">
+        <v>0.9998258787187658</v>
+      </c>
+      <c r="J22" s="50" t="n">
+        <v>0.9998258787187658</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:L36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -735,11 +1470,11 @@
         <f>Data!B2</f>
         <v/>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="51">
         <f>Data!Z2</f>
         <v/>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="52">
         <f>Data!AA2</f>
         <v/>
       </c>
@@ -785,11 +1520,11 @@
         <f>Data!B3</f>
         <v/>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="51">
         <f>Data!Z3</f>
         <v/>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="52">
         <f>Data!AA3</f>
         <v/>
       </c>
@@ -835,11 +1570,11 @@
         <f>Data!B4</f>
         <v/>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="51">
         <f>Data!Z4</f>
         <v/>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="52">
         <f>Data!AA4</f>
         <v/>
       </c>
@@ -885,11 +1620,11 @@
         <f>Data!B5</f>
         <v/>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="51">
         <f>Data!Z5</f>
         <v/>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="52">
         <f>Data!AA5</f>
         <v/>
       </c>
@@ -935,11 +1670,11 @@
         <f>Data!B6</f>
         <v/>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="53">
         <f>Data!Z6</f>
         <v/>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="54">
         <f>Data!AA6</f>
         <v/>
       </c>
@@ -985,11 +1720,11 @@
         <f>Data!B7</f>
         <v/>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="53">
         <f>Data!Z7</f>
         <v/>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="54">
         <f>Data!AA7</f>
         <v/>
       </c>
@@ -1035,11 +1770,11 @@
         <f>Data!B8</f>
         <v/>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="53">
         <f>Data!Z8</f>
         <v/>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="54">
         <f>Data!AA8</f>
         <v/>
       </c>
@@ -1085,11 +1820,11 @@
         <f>Data!B9</f>
         <v/>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="53">
         <f>Data!Z9</f>
         <v/>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="54">
         <f>Data!AA9</f>
         <v/>
       </c>
@@ -1135,11 +1870,11 @@
         <f>Data!B10</f>
         <v/>
       </c>
-      <c r="C13" s="16">
+      <c r="C13" s="55">
         <f>Data!Z10</f>
         <v/>
       </c>
-      <c r="D13" s="17">
+      <c r="D13" s="56">
         <f>Data!AA10</f>
         <v/>
       </c>
@@ -1185,11 +1920,11 @@
         <f>Data!B11</f>
         <v/>
       </c>
-      <c r="C14" s="16">
+      <c r="C14" s="55">
         <f>Data!Z11</f>
         <v/>
       </c>
-      <c r="D14" s="17">
+      <c r="D14" s="56">
         <f>Data!AA11</f>
         <v/>
       </c>
@@ -1235,11 +1970,11 @@
         <f>Data!B12</f>
         <v/>
       </c>
-      <c r="C15" s="16">
+      <c r="C15" s="55">
         <f>Data!Z12</f>
         <v/>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="56">
         <f>Data!AA12</f>
         <v/>
       </c>
@@ -1285,11 +2020,11 @@
         <f>Data!B13</f>
         <v/>
       </c>
-      <c r="C16" s="16">
+      <c r="C16" s="55">
         <f>Data!Z13</f>
         <v/>
       </c>
-      <c r="D16" s="17">
+      <c r="D16" s="56">
         <f>Data!AA13</f>
         <v/>
       </c>
@@ -1335,11 +2070,11 @@
         <f>Data!B14</f>
         <v/>
       </c>
-      <c r="C17" s="21">
+      <c r="C17" s="57">
         <f>Data!Z14</f>
         <v/>
       </c>
-      <c r="D17" s="22">
+      <c r="D17" s="58">
         <f>Data!AA14</f>
         <v/>
       </c>
@@ -1385,11 +2120,11 @@
         <f>Data!B15</f>
         <v/>
       </c>
-      <c r="C18" s="21">
+      <c r="C18" s="57">
         <f>Data!Z15</f>
         <v/>
       </c>
-      <c r="D18" s="22">
+      <c r="D18" s="58">
         <f>Data!AA15</f>
         <v/>
       </c>
@@ -1435,11 +2170,11 @@
         <f>Data!B16</f>
         <v/>
       </c>
-      <c r="C19" s="21">
+      <c r="C19" s="57">
         <f>Data!Z16</f>
         <v/>
       </c>
-      <c r="D19" s="22">
+      <c r="D19" s="58">
         <f>Data!AA16</f>
         <v/>
       </c>
@@ -1485,11 +2220,11 @@
         <f>Data!B17</f>
         <v/>
       </c>
-      <c r="C20" s="21">
+      <c r="C20" s="57">
         <f>Data!Z17</f>
         <v/>
       </c>
-      <c r="D20" s="22">
+      <c r="D20" s="58">
         <f>Data!AA17</f>
         <v/>
       </c>
@@ -1535,11 +2270,11 @@
         <f>Data!B18</f>
         <v/>
       </c>
-      <c r="C21" s="26">
+      <c r="C21" s="59">
         <f>Data!Z18</f>
         <v/>
       </c>
-      <c r="D21" s="27">
+      <c r="D21" s="60">
         <f>Data!AA18</f>
         <v/>
       </c>
@@ -1585,11 +2320,11 @@
         <f>Data!B19</f>
         <v/>
       </c>
-      <c r="C22" s="26">
+      <c r="C22" s="59">
         <f>Data!Z19</f>
         <v/>
       </c>
-      <c r="D22" s="27">
+      <c r="D22" s="60">
         <f>Data!AA19</f>
         <v/>
       </c>
@@ -1635,11 +2370,11 @@
         <f>Data!B20</f>
         <v/>
       </c>
-      <c r="C23" s="26">
+      <c r="C23" s="59">
         <f>Data!Z20</f>
         <v/>
       </c>
-      <c r="D23" s="27">
+      <c r="D23" s="60">
         <f>Data!AA20</f>
         <v/>
       </c>
@@ -1685,11 +2420,11 @@
         <f>Data!B21</f>
         <v/>
       </c>
-      <c r="C24" s="26">
+      <c r="C24" s="59">
         <f>Data!Z21</f>
         <v/>
       </c>
-      <c r="D24" s="27">
+      <c r="D24" s="60">
         <f>Data!AA21</f>
         <v/>
       </c>
@@ -1735,11 +2470,11 @@
         <f>Data!B22</f>
         <v/>
       </c>
-      <c r="C25" s="26">
+      <c r="C25" s="59">
         <f>Data!Z22</f>
         <v/>
       </c>
-      <c r="D25" s="27">
+      <c r="D25" s="60">
         <f>Data!AA22</f>
         <v/>
       </c>
@@ -1847,7 +2582,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1905,7 +2640,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2627,7 +3362,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2960,13 +3695,13 @@
           <t>RS-68A (gimballed)</t>
         </is>
       </c>
-      <c r="F2" s="36" t="n">
+      <c r="F2" s="61" t="n">
         <v>3123000</v>
       </c>
       <c r="G2" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="H2" s="37">
+      <c r="H2" s="62">
         <f>IFERROR(F2*G2,"n/d")</f>
         <v/>
       </c>
@@ -2975,13 +3710,13 @@
           <t>None at vehicle level</t>
         </is>
       </c>
-      <c r="J2" s="36" t="n">
+      <c r="J2" s="61" t="n">
         <v>0</v>
       </c>
       <c r="K2" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="L2" s="37">
+      <c r="L2" s="62">
         <f>IFERROR(J2*K2,"n/d")</f>
         <v/>
       </c>
@@ -2990,21 +3725,21 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N2" s="36" t="n">
+      <c r="N2" s="61" t="n">
         <v>0</v>
       </c>
       <c r="O2" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="P2" s="37">
+      <c r="P2" s="62">
         <f>IFERROR(N2*O2,"n/d")</f>
         <v/>
       </c>
-      <c r="Q2" s="38">
+      <c r="Q2" s="63">
         <f>IFERROR(H2+L2+P2,"incomplete")</f>
         <v/>
       </c>
-      <c r="R2" s="38">
+      <c r="R2" s="63">
         <f>IF(A2="Boosters",SUM(H2,P2),SUM(H2,L2,P2))</f>
         <v/>
       </c>
@@ -3012,38 +3747,38 @@
         <f>IF(A2="Boosters",IF(AND(ISNUMBER(H2),ISNUMBER(P2)),"complete","PARTIAL"),IF(ISNUMBER(Q2),"complete","PARTIAL"))</f>
         <v/>
       </c>
-      <c r="T2" s="39" t="n">
+      <c r="T2" s="64" t="n">
         <v>725700</v>
       </c>
-      <c r="U2" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" s="40">
+      <c r="U2" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" s="65">
         <f>IFERROR(T2-U2,"n/d")</f>
         <v/>
       </c>
-      <c r="W2" s="39" t="inlineStr">
+      <c r="W2" s="64" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="X2" s="40">
+      <c r="X2" s="65">
         <f>IFERROR(V2-W2,"n/d")</f>
         <v/>
       </c>
-      <c r="Y2" s="40">
+      <c r="Y2" s="65">
         <f>IFERROR(V2*g0,"n/d")</f>
         <v/>
       </c>
-      <c r="Z2" s="41">
+      <c r="Z2" s="66">
         <f>IF(AND(S2="PARTIAL",R2=0),"n/d",IFERROR(R2/Y2,"n/d"))</f>
         <v/>
       </c>
-      <c r="AA2" s="42">
+      <c r="AA2" s="67">
         <f>IFERROR(X2/V2,"n/d")</f>
         <v/>
       </c>
-      <c r="AB2" s="43">
+      <c r="AB2" s="68">
         <f>IFERROR(V2/W2,IFERROR(V2/(V2-X2),"n/d"))</f>
         <v/>
       </c>
@@ -3164,13 +3899,13 @@
           <t>Vulcain 2 (gimballed, sea level)</t>
         </is>
       </c>
-      <c r="F3" s="36" t="n">
+      <c r="F3" s="61" t="n">
         <v>960000</v>
       </c>
       <c r="G3" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="H3" s="37">
+      <c r="H3" s="62">
         <f>IFERROR(F3*G3,"n/d")</f>
         <v/>
       </c>
@@ -3179,13 +3914,13 @@
           <t>None at vehicle level</t>
         </is>
       </c>
-      <c r="J3" s="36" t="n">
+      <c r="J3" s="61" t="n">
         <v>0</v>
       </c>
       <c r="K3" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="L3" s="37">
+      <c r="L3" s="62">
         <f>IFERROR(J3*K3,"n/d")</f>
         <v/>
       </c>
@@ -3194,21 +3929,21 @@
           <t>EAP P241 solid booster</t>
         </is>
       </c>
-      <c r="N3" s="36" t="n">
+      <c r="N3" s="61" t="n">
         <v>7080000</v>
       </c>
       <c r="O3" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="P3" s="37">
+      <c r="P3" s="62">
         <f>IFERROR(N3*O3,"n/d")</f>
         <v/>
       </c>
-      <c r="Q3" s="38">
+      <c r="Q3" s="63">
         <f>IFERROR(H3+L3+P3,"incomplete")</f>
         <v/>
       </c>
-      <c r="R3" s="38">
+      <c r="R3" s="63">
         <f>IF(A3="Boosters",SUM(H3,P3),SUM(H3,L3,P3))</f>
         <v/>
       </c>
@@ -3216,38 +3951,38 @@
         <f>IF(A3="Boosters",IF(AND(ISNUMBER(H3),ISNUMBER(P3)),"complete","PARTIAL"),IF(ISNUMBER(Q3),"complete","PARTIAL"))</f>
         <v/>
       </c>
-      <c r="T3" s="39" t="n">
+      <c r="T3" s="64" t="n">
         <v>780000</v>
       </c>
-      <c r="U3" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" s="40">
+      <c r="U3" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="65">
         <f>IFERROR(T3-U3,"n/d")</f>
         <v/>
       </c>
-      <c r="W3" s="39" t="inlineStr">
+      <c r="W3" s="64" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="X3" s="40">
+      <c r="X3" s="65">
         <f>IFERROR(V3-W3,"n/d")</f>
         <v/>
       </c>
-      <c r="Y3" s="40">
+      <c r="Y3" s="65">
         <f>IFERROR(V3*g0,"n/d")</f>
         <v/>
       </c>
-      <c r="Z3" s="41">
+      <c r="Z3" s="66">
         <f>IF(AND(S3="PARTIAL",R3=0),"n/d",IFERROR(R3/Y3,"n/d"))</f>
         <v/>
       </c>
-      <c r="AA3" s="42">
+      <c r="AA3" s="67">
         <f>IFERROR(X3/V3,"n/d")</f>
         <v/>
       </c>
-      <c r="AB3" s="43">
+      <c r="AB3" s="68">
         <f>IFERROR(V3/W3,IFERROR(V3/(V3-X3),"n/d"))</f>
         <v/>
       </c>
@@ -3368,13 +4103,13 @@
           <t>P120C solid motor (max thrust)</t>
         </is>
       </c>
-      <c r="F4" s="36" t="n">
+      <c r="F4" s="61" t="n">
         <v>4650000</v>
       </c>
       <c r="G4" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="H4" s="37">
+      <c r="H4" s="62">
         <f>IFERROR(F4*G4,"n/d")</f>
         <v/>
       </c>
@@ -3383,13 +4118,13 @@
           <t>None at vehicle level</t>
         </is>
       </c>
-      <c r="J4" s="36" t="n">
+      <c r="J4" s="61" t="n">
         <v>0</v>
       </c>
       <c r="K4" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="L4" s="37">
+      <c r="L4" s="62">
         <f>IFERROR(J4*K4,"n/d")</f>
         <v/>
       </c>
@@ -3398,21 +4133,21 @@
           <t>None (single-body vehicle, no strap-ons)</t>
         </is>
       </c>
-      <c r="N4" s="36" t="n">
+      <c r="N4" s="61" t="n">
         <v>0</v>
       </c>
       <c r="O4" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="P4" s="37">
+      <c r="P4" s="62">
         <f>IFERROR(N4*O4,"n/d")</f>
         <v/>
       </c>
-      <c r="Q4" s="38">
+      <c r="Q4" s="63">
         <f>IFERROR(H4+L4+P4,"incomplete")</f>
         <v/>
       </c>
-      <c r="R4" s="38">
+      <c r="R4" s="63">
         <f>IF(A4="Boosters",SUM(H4,P4),SUM(H4,L4,P4))</f>
         <v/>
       </c>
@@ -3420,38 +4155,38 @@
         <f>IF(A4="Boosters",IF(AND(ISNUMBER(H4),ISNUMBER(P4)),"complete","PARTIAL"),IF(ISNUMBER(Q4),"complete","PARTIAL"))</f>
         <v/>
       </c>
-      <c r="T4" s="39" t="n">
+      <c r="T4" s="64" t="n">
         <v>210000</v>
       </c>
-      <c r="U4" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="40">
+      <c r="U4" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="65">
         <f>IFERROR(T4-U4,"n/d")</f>
         <v/>
       </c>
-      <c r="W4" s="39" t="inlineStr">
+      <c r="W4" s="64" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="X4" s="40">
+      <c r="X4" s="65">
         <f>IFERROR(V4-W4,"n/d")</f>
         <v/>
       </c>
-      <c r="Y4" s="40">
+      <c r="Y4" s="65">
         <f>IFERROR(V4*g0,"n/d")</f>
         <v/>
       </c>
-      <c r="Z4" s="41">
+      <c r="Z4" s="66">
         <f>IF(AND(S4="PARTIAL",R4=0),"n/d",IFERROR(R4/Y4,"n/d"))</f>
         <v/>
       </c>
-      <c r="AA4" s="42">
+      <c r="AA4" s="67">
         <f>IFERROR(X4/V4,"n/d")</f>
         <v/>
       </c>
-      <c r="AB4" s="43">
+      <c r="AB4" s="68">
         <f>IFERROR(V4/W4,IFERROR(V4/(V4-X4),"n/d"))</f>
         <v/>
       </c>
@@ -3572,13 +4307,13 @@
           <t>P80 solid motor</t>
         </is>
       </c>
-      <c r="F5" s="36" t="n">
+      <c r="F5" s="61" t="n">
         <v>2942000</v>
       </c>
       <c r="G5" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="H5" s="37">
+      <c r="H5" s="62">
         <f>IFERROR(F5*G5,"n/d")</f>
         <v/>
       </c>
@@ -3587,13 +4322,13 @@
           <t>None at vehicle level</t>
         </is>
       </c>
-      <c r="J5" s="36" t="n">
+      <c r="J5" s="61" t="n">
         <v>0</v>
       </c>
       <c r="K5" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="37">
+      <c r="L5" s="62">
         <f>IFERROR(J5*K5,"n/d")</f>
         <v/>
       </c>
@@ -3602,21 +4337,21 @@
           <t>None (single-body vehicle, no strap-ons)</t>
         </is>
       </c>
-      <c r="N5" s="36" t="n">
+      <c r="N5" s="61" t="n">
         <v>0</v>
       </c>
       <c r="O5" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="P5" s="37">
+      <c r="P5" s="62">
         <f>IFERROR(N5*O5,"n/d")</f>
         <v/>
       </c>
-      <c r="Q5" s="38">
+      <c r="Q5" s="63">
         <f>IFERROR(H5+L5+P5,"incomplete")</f>
         <v/>
       </c>
-      <c r="R5" s="38">
+      <c r="R5" s="63">
         <f>IF(A5="Boosters",SUM(H5,P5),SUM(H5,L5,P5))</f>
         <v/>
       </c>
@@ -3624,38 +4359,38 @@
         <f>IF(A5="Boosters",IF(AND(ISNUMBER(H5),ISNUMBER(P5)),"complete","PARTIAL"),IF(ISNUMBER(Q5),"complete","PARTIAL"))</f>
         <v/>
       </c>
-      <c r="T5" s="39" t="n">
+      <c r="T5" s="64" t="n">
         <v>137000</v>
       </c>
-      <c r="U5" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="40">
+      <c r="U5" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="65">
         <f>IFERROR(T5-U5,"n/d")</f>
         <v/>
       </c>
-      <c r="W5" s="39" t="inlineStr">
+      <c r="W5" s="64" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="X5" s="40">
+      <c r="X5" s="65">
         <f>IFERROR(V5-W5,"n/d")</f>
         <v/>
       </c>
-      <c r="Y5" s="40">
+      <c r="Y5" s="65">
         <f>IFERROR(V5*g0,"n/d")</f>
         <v/>
       </c>
-      <c r="Z5" s="41">
+      <c r="Z5" s="66">
         <f>IF(AND(S5="PARTIAL",R5=0),"n/d",IFERROR(R5/Y5,"n/d"))</f>
         <v/>
       </c>
-      <c r="AA5" s="42">
+      <c r="AA5" s="67">
         <f>IFERROR(X5/V5,"n/d")</f>
         <v/>
       </c>
-      <c r="AB5" s="43">
+      <c r="AB5" s="68">
         <f>IFERROR(V5/W5,IFERROR(V5/(V5-X5),"n/d"))</f>
         <v/>
       </c>
@@ -3776,13 +4511,13 @@
           <t>40 mN cold-gas orbit-control thruster (rear panel)</t>
         </is>
       </c>
-      <c r="F6" s="36" t="n">
+      <c r="F6" s="61" t="n">
         <v>0.04</v>
       </c>
       <c r="G6" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="H6" s="37">
+      <c r="H6" s="62">
         <f>IFERROR(F6*G6,"n/d")</f>
         <v/>
       </c>
@@ -3791,13 +4526,13 @@
           <t>10 mN cold-gas attitude thruster (2 on each of 6 faces)</t>
         </is>
       </c>
-      <c r="J6" s="36" t="n">
+      <c r="J6" s="61" t="n">
         <v>0.01</v>
       </c>
       <c r="K6" s="35" t="n">
         <v>12</v>
       </c>
-      <c r="L6" s="37">
+      <c r="L6" s="62">
         <f>IFERROR(J6*K6,"n/d")</f>
         <v/>
       </c>
@@ -3806,21 +4541,21 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N6" s="36" t="n">
+      <c r="N6" s="61" t="n">
         <v>0</v>
       </c>
       <c r="O6" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="P6" s="37">
+      <c r="P6" s="62">
         <f>IFERROR(N6*O6,"n/d")</f>
         <v/>
       </c>
-      <c r="Q6" s="38">
+      <c r="Q6" s="63">
         <f>IFERROR(H6+L6+P6,"incomplete")</f>
         <v/>
       </c>
-      <c r="R6" s="38">
+      <c r="R6" s="63">
         <f>IF(A6="Boosters",SUM(H6,P6),SUM(H6,L6,P6))</f>
         <v/>
       </c>
@@ -3828,33 +4563,33 @@
         <f>IF(A6="Boosters",IF(AND(ISNUMBER(H6),ISNUMBER(P6)),"complete","PARTIAL"),IF(ISNUMBER(Q6),"complete","PARTIAL"))</f>
         <v/>
       </c>
-      <c r="T6" s="39" t="n">
+      <c r="T6" s="64" t="n">
         <v>600.2</v>
       </c>
-      <c r="U6" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="40">
+      <c r="U6" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="65">
         <f>IFERROR(T6-U6,"n/d")</f>
         <v/>
       </c>
-      <c r="W6" s="39" t="n"/>
-      <c r="X6" s="40" t="n">
+      <c r="W6" s="64" t="n"/>
+      <c r="X6" s="65" t="n">
         <v>31.3</v>
       </c>
-      <c r="Y6" s="40">
+      <c r="Y6" s="65">
         <f>IFERROR(V6*g0,"n/d")</f>
         <v/>
       </c>
-      <c r="Z6" s="41">
+      <c r="Z6" s="66">
         <f>IF(AND(S6="PARTIAL",R6=0),"n/d",IFERROR(R6/Y6,"n/d"))</f>
         <v/>
       </c>
-      <c r="AA6" s="42">
+      <c r="AA6" s="67">
         <f>IFERROR(X6/V6,"n/d")</f>
         <v/>
       </c>
-      <c r="AB6" s="43">
+      <c r="AB6" s="68">
         <f>IFERROR(V6/W6,IFERROR(V6/(V6-X6),"n/d"))</f>
         <v/>
       </c>
@@ -3975,13 +4710,13 @@
           <t>None (no main/apogee engine)</t>
         </is>
       </c>
-      <c r="F7" s="36" t="n">
+      <c r="F7" s="61" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="37">
+      <c r="H7" s="62">
         <f>IFERROR(F7*G7,"n/d")</f>
         <v/>
       </c>
@@ -3990,13 +4725,13 @@
           <t>1 N hydrazine monopropellant thruster</t>
         </is>
       </c>
-      <c r="J7" s="36" t="n">
+      <c r="J7" s="61" t="n">
         <v>1</v>
       </c>
       <c r="K7" s="35" t="n">
         <v>8</v>
       </c>
-      <c r="L7" s="37">
+      <c r="L7" s="62">
         <f>IFERROR(J7*K7,"n/d")</f>
         <v/>
       </c>
@@ -4005,21 +4740,21 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N7" s="36" t="n">
+      <c r="N7" s="61" t="n">
         <v>0</v>
       </c>
       <c r="O7" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="P7" s="37">
+      <c r="P7" s="62">
         <f>IFERROR(N7*O7,"n/d")</f>
         <v/>
       </c>
-      <c r="Q7" s="38">
+      <c r="Q7" s="63">
         <f>IFERROR(H7+L7+P7,"incomplete")</f>
         <v/>
       </c>
-      <c r="R7" s="38">
+      <c r="R7" s="63">
         <f>IF(A7="Boosters",SUM(H7,P7),SUM(H7,L7,P7))</f>
         <v/>
       </c>
@@ -4027,38 +4762,38 @@
         <f>IF(A7="Boosters",IF(AND(ISNUMBER(H7),ISNUMBER(P7)),"complete","PARTIAL"),IF(ISNUMBER(Q7),"complete","PARTIAL"))</f>
         <v/>
       </c>
-      <c r="T7" s="39" t="n">
+      <c r="T7" s="64" t="n">
         <v>1250</v>
       </c>
-      <c r="U7" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="40">
+      <c r="U7" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="65">
         <f>IFERROR(T7-U7,"n/d")</f>
         <v/>
       </c>
-      <c r="W7" s="39" t="inlineStr">
+      <c r="W7" s="64" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="X7" s="40">
+      <c r="X7" s="65">
         <f>IFERROR(V7-W7,"n/d")</f>
         <v/>
       </c>
-      <c r="Y7" s="40">
+      <c r="Y7" s="65">
         <f>IFERROR(V7*g0,"n/d")</f>
         <v/>
       </c>
-      <c r="Z7" s="41">
+      <c r="Z7" s="66">
         <f>IF(AND(S7="PARTIAL",R7=0),"n/d",IFERROR(R7/Y7,"n/d"))</f>
         <v/>
       </c>
-      <c r="AA7" s="42">
+      <c r="AA7" s="67">
         <f>IFERROR(X7/V7,"n/d")</f>
         <v/>
       </c>
-      <c r="AB7" s="43">
+      <c r="AB7" s="68">
         <f>IFERROR(V7/W7,IFERROR(V7/(V7-X7),"n/d"))</f>
         <v/>
       </c>
@@ -4181,13 +4916,13 @@
           <t>None (no main engine)</t>
         </is>
       </c>
-      <c r="F8" s="36" t="n">
+      <c r="F8" s="61" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="37">
+      <c r="H8" s="62">
         <f>IFERROR(F8*G8,"n/d")</f>
         <v/>
       </c>
@@ -4196,13 +4931,13 @@
           <t>4.5 N hydrazine monopropellant thruster (MONARC-5)</t>
         </is>
       </c>
-      <c r="J8" s="36" t="n">
+      <c r="J8" s="61" t="n">
         <v>4.5</v>
       </c>
       <c r="K8" s="35" t="n">
         <v>8</v>
       </c>
-      <c r="L8" s="37">
+      <c r="L8" s="62">
         <f>IFERROR(J8*K8,"n/d")</f>
         <v/>
       </c>
@@ -4211,21 +4946,21 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N8" s="36" t="n">
+      <c r="N8" s="61" t="n">
         <v>0</v>
       </c>
       <c r="O8" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="P8" s="37">
+      <c r="P8" s="62">
         <f>IFERROR(N8*O8,"n/d")</f>
         <v/>
       </c>
-      <c r="Q8" s="38">
+      <c r="Q8" s="63">
         <f>IFERROR(H8+L8+P8,"incomplete")</f>
         <v/>
       </c>
-      <c r="R8" s="38">
+      <c r="R8" s="63">
         <f>IF(A8="Boosters",SUM(H8,P8),SUM(H8,L8,P8))</f>
         <v/>
       </c>
@@ -4233,39 +4968,39 @@
         <f>IF(A8="Boosters",IF(AND(ISNUMBER(H8),ISNUMBER(P8)),"complete","PARTIAL"),IF(ISNUMBER(Q8),"complete","PARTIAL"))</f>
         <v/>
       </c>
-      <c r="T8" s="39" t="inlineStr">
+      <c r="T8" s="64" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="U8" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="40">
+      <c r="U8" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="65">
         <f>IFERROR(T8-U8,"n/d")</f>
         <v/>
       </c>
-      <c r="W8" s="39" t="inlineStr">
+      <c r="W8" s="64" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="X8" s="40" t="n">
+      <c r="X8" s="65" t="n">
         <v>80</v>
       </c>
-      <c r="Y8" s="40">
+      <c r="Y8" s="65">
         <f>IFERROR(V8*g0,"n/d")</f>
         <v/>
       </c>
-      <c r="Z8" s="41">
+      <c r="Z8" s="66">
         <f>IF(AND(S8="PARTIAL",R8=0),"n/d",IFERROR(R8/Y8,"n/d"))</f>
         <v/>
       </c>
-      <c r="AA8" s="42">
+      <c r="AA8" s="67">
         <f>IFERROR(X8/V8,"n/d")</f>
         <v/>
       </c>
-      <c r="AB8" s="43">
+      <c r="AB8" s="68">
         <f>IFERROR(V8/W8,IFERROR(V8/(V8-X8),"n/d"))</f>
         <v/>
       </c>
@@ -4388,13 +5123,13 @@
           <t>None (no main/apogee engine)</t>
         </is>
       </c>
-      <c r="F9" s="36" t="n">
+      <c r="F9" s="61" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="37">
+      <c r="H9" s="62">
         <f>IFERROR(F9*G9,"n/d")</f>
         <v/>
       </c>
@@ -4403,7 +5138,7 @@
           <t>Catalytic hydrazine monopropellant thruster</t>
         </is>
       </c>
-      <c r="J9" s="36" t="inlineStr">
+      <c r="J9" s="61" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
@@ -4413,7 +5148,7 @@
           <t>n/d</t>
         </is>
       </c>
-      <c r="L9" s="37">
+      <c r="L9" s="62">
         <f>IFERROR(J9*K9,"n/d")</f>
         <v/>
       </c>
@@ -4422,21 +5157,21 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N9" s="36" t="n">
+      <c r="N9" s="61" t="n">
         <v>0</v>
       </c>
       <c r="O9" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="P9" s="37">
+      <c r="P9" s="62">
         <f>IFERROR(N9*O9,"n/d")</f>
         <v/>
       </c>
-      <c r="Q9" s="38">
+      <c r="Q9" s="63">
         <f>IFERROR(H9+L9+P9,"incomplete")</f>
         <v/>
       </c>
-      <c r="R9" s="38">
+      <c r="R9" s="63">
         <f>IF(A9="Boosters",SUM(H9,P9),SUM(H9,L9,P9))</f>
         <v/>
       </c>
@@ -4444,37 +5179,37 @@
         <f>IF(A9="Boosters",IF(AND(ISNUMBER(H9),ISNUMBER(P9)),"complete","PARTIAL"),IF(ISNUMBER(Q9),"complete","PARTIAL"))</f>
         <v/>
       </c>
-      <c r="T9" s="39" t="n">
+      <c r="T9" s="64" t="n">
         <v>2300</v>
       </c>
-      <c r="U9" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="40">
+      <c r="U9" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="65">
         <f>IFERROR(T9-U9,"n/d")</f>
         <v/>
       </c>
-      <c r="W9" s="39" t="inlineStr">
+      <c r="W9" s="64" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="X9" s="40" t="n">
+      <c r="X9" s="65" t="n">
         <v>130</v>
       </c>
-      <c r="Y9" s="40">
+      <c r="Y9" s="65">
         <f>IFERROR(V9*g0,"n/d")</f>
         <v/>
       </c>
-      <c r="Z9" s="41">
+      <c r="Z9" s="66">
         <f>IF(AND(S9="PARTIAL",R9=0),"n/d",IFERROR(R9/Y9,"n/d"))</f>
         <v/>
       </c>
-      <c r="AA9" s="42">
+      <c r="AA9" s="67">
         <f>IFERROR(X9/V9,"n/d")</f>
         <v/>
       </c>
-      <c r="AB9" s="43">
+      <c r="AB9" s="68">
         <f>IFERROR(V9/W9,IFERROR(V9/(V9-X9),"n/d"))</f>
         <v/>
       </c>
@@ -4595,13 +5330,13 @@
           <t>Aerojet R-4D bipropellant main engine, 110 lbf</t>
         </is>
       </c>
-      <c r="F10" s="36" t="n">
+      <c r="F10" s="61" t="n">
         <v>489.3</v>
       </c>
       <c r="G10" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="37">
+      <c r="H10" s="62">
         <f>IFERROR(F10*G10,"n/d")</f>
         <v/>
       </c>
@@ -4610,13 +5345,13 @@
           <t>AMPAC-ISP attitude control thruster, 5 lbf, in four pairs</t>
         </is>
       </c>
-      <c r="J10" s="36" t="n">
+      <c r="J10" s="61" t="n">
         <v>22.24</v>
       </c>
       <c r="K10" s="35" t="n">
         <v>8</v>
       </c>
-      <c r="L10" s="37">
+      <c r="L10" s="62">
         <f>IFERROR(J10*K10,"n/d")</f>
         <v/>
       </c>
@@ -4625,21 +5360,21 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N10" s="36" t="n">
+      <c r="N10" s="61" t="n">
         <v>0</v>
       </c>
       <c r="O10" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="P10" s="37">
+      <c r="P10" s="62">
         <f>IFERROR(N10*O10,"n/d")</f>
         <v/>
       </c>
-      <c r="Q10" s="38">
+      <c r="Q10" s="63">
         <f>IFERROR(H10+L10+P10,"incomplete")</f>
         <v/>
       </c>
-      <c r="R10" s="38">
+      <c r="R10" s="63">
         <f>IF(A10="Boosters",SUM(H10,P10),SUM(H10,L10,P10))</f>
         <v/>
       </c>
@@ -4647,37 +5382,37 @@
         <f>IF(A10="Boosters",IF(AND(ISNUMBER(H10),ISNUMBER(P10)),"complete","PARTIAL"),IF(ISNUMBER(Q10),"complete","PARTIAL"))</f>
         <v/>
       </c>
-      <c r="T10" s="39" t="n">
+      <c r="T10" s="64" t="n">
         <v>3100</v>
       </c>
-      <c r="U10" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="40">
+      <c r="U10" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="65">
         <f>IFERROR(T10-U10,"n/d")</f>
         <v/>
       </c>
-      <c r="W10" s="39" t="inlineStr">
+      <c r="W10" s="64" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="X10" s="40" t="n">
+      <c r="X10" s="65" t="n">
         <v>1450</v>
       </c>
-      <c r="Y10" s="40">
+      <c r="Y10" s="65">
         <f>IFERROR(V10*g0,"n/d")</f>
         <v/>
       </c>
-      <c r="Z10" s="41">
+      <c r="Z10" s="66">
         <f>IF(AND(S10="PARTIAL",R10=0),"n/d",IFERROR(R10/Y10,"n/d"))</f>
         <v/>
       </c>
-      <c r="AA10" s="42">
+      <c r="AA10" s="67">
         <f>IFERROR(X10/V10,"n/d")</f>
         <v/>
       </c>
-      <c r="AB10" s="43">
+      <c r="AB10" s="68">
         <f>IFERROR(V10/W10,IFERROR(V10/(V10-X10),"n/d"))</f>
         <v/>
       </c>
@@ -4798,13 +5533,13 @@
           <t>Liquid Apogee Motor (LAM), 400 N</t>
         </is>
       </c>
-      <c r="F11" s="36" t="n">
+      <c r="F11" s="61" t="n">
         <v>400</v>
       </c>
       <c r="G11" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="H11" s="37">
+      <c r="H11" s="62">
         <f>IFERROR(F11*G11,"n/d")</f>
         <v/>
       </c>
@@ -4813,13 +5548,13 @@
           <t>Reaction Control Thruster (RCT), 10 N</t>
         </is>
       </c>
-      <c r="J11" s="36" t="n">
+      <c r="J11" s="61" t="n">
         <v>10</v>
       </c>
       <c r="K11" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="L11" s="37">
+      <c r="L11" s="62">
         <f>IFERROR(J11*K11,"n/d")</f>
         <v/>
       </c>
@@ -4828,21 +5563,21 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N11" s="36" t="n">
+      <c r="N11" s="61" t="n">
         <v>0</v>
       </c>
       <c r="O11" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="P11" s="37">
+      <c r="P11" s="62">
         <f>IFERROR(N11*O11,"n/d")</f>
         <v/>
       </c>
-      <c r="Q11" s="38">
+      <c r="Q11" s="63">
         <f>IFERROR(H11+L11+P11,"incomplete")</f>
         <v/>
       </c>
-      <c r="R11" s="38">
+      <c r="R11" s="63">
         <f>IF(A11="Boosters",SUM(H11,P11),SUM(H11,L11,P11))</f>
         <v/>
       </c>
@@ -4850,37 +5585,37 @@
         <f>IF(A11="Boosters",IF(AND(ISNUMBER(H11),ISNUMBER(P11)),"complete","PARTIAL"),IF(ISNUMBER(Q11),"complete","PARTIAL"))</f>
         <v/>
       </c>
-      <c r="T11" s="39" t="n">
+      <c r="T11" s="64" t="n">
         <v>2000</v>
       </c>
-      <c r="U11" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="40">
+      <c r="U11" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="65">
         <f>IFERROR(T11-U11,"n/d")</f>
         <v/>
       </c>
-      <c r="W11" s="39" t="inlineStr">
+      <c r="W11" s="64" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="X11" s="40" t="n">
+      <c r="X11" s="65" t="n">
         <v>976</v>
       </c>
-      <c r="Y11" s="40">
+      <c r="Y11" s="65">
         <f>IFERROR(V11*g0,"n/d")</f>
         <v/>
       </c>
-      <c r="Z11" s="41">
+      <c r="Z11" s="66">
         <f>IF(AND(S11="PARTIAL",R11=0),"n/d",IFERROR(R11/Y11,"n/d"))</f>
         <v/>
       </c>
-      <c r="AA11" s="42">
+      <c r="AA11" s="67">
         <f>IFERROR(X11/V11,"n/d")</f>
         <v/>
       </c>
-      <c r="AB11" s="43">
+      <c r="AB11" s="68">
         <f>IFERROR(V11/W11,IFERROR(V11/(V11-X11),"n/d"))</f>
         <v/>
       </c>
@@ -5001,7 +5736,7 @@
           <t>Liquid apogee engine (Lockheed Martin A2100A bus)</t>
         </is>
       </c>
-      <c r="F12" s="36" t="inlineStr">
+      <c r="F12" s="61" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
@@ -5011,7 +5746,7 @@
           <t>n/d</t>
         </is>
       </c>
-      <c r="H12" s="37">
+      <c r="H12" s="62">
         <f>IFERROR(F12*G12,"n/d")</f>
         <v/>
       </c>
@@ -5020,7 +5755,7 @@
           <t>Chemical RCS thrusters</t>
         </is>
       </c>
-      <c r="J12" s="36" t="inlineStr">
+      <c r="J12" s="61" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
@@ -5030,7 +5765,7 @@
           <t>n/d</t>
         </is>
       </c>
-      <c r="L12" s="37">
+      <c r="L12" s="62">
         <f>IFERROR(J12*K12,"n/d")</f>
         <v/>
       </c>
@@ -5039,21 +5774,21 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N12" s="36" t="n">
+      <c r="N12" s="61" t="n">
         <v>0</v>
       </c>
       <c r="O12" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="P12" s="37">
+      <c r="P12" s="62">
         <f>IFERROR(N12*O12,"n/d")</f>
         <v/>
       </c>
-      <c r="Q12" s="38">
+      <c r="Q12" s="63">
         <f>IFERROR(H12+L12+P12,"incomplete")</f>
         <v/>
       </c>
-      <c r="R12" s="38">
+      <c r="R12" s="63">
         <f>IF(A12="Boosters",SUM(H12,P12),SUM(H12,L12,P12))</f>
         <v/>
       </c>
@@ -5061,36 +5796,36 @@
         <f>IF(A12="Boosters",IF(AND(ISNUMBER(H12),ISNUMBER(P12)),"complete","PARTIAL"),IF(ISNUMBER(Q12),"complete","PARTIAL"))</f>
         <v/>
       </c>
-      <c r="T12" s="39" t="n">
+      <c r="T12" s="64" t="n">
         <v>5192</v>
       </c>
-      <c r="U12" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="40">
+      <c r="U12" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="65">
         <f>IFERROR(T12-U12,"n/d")</f>
         <v/>
       </c>
-      <c r="W12" s="39" t="n">
+      <c r="W12" s="64" t="n">
         <v>2857</v>
       </c>
-      <c r="X12" s="40">
+      <c r="X12" s="65">
         <f>IFERROR(V12-W12,"n/d")</f>
         <v/>
       </c>
-      <c r="Y12" s="40">
+      <c r="Y12" s="65">
         <f>IFERROR(V12*g0,"n/d")</f>
         <v/>
       </c>
-      <c r="Z12" s="41">
+      <c r="Z12" s="66">
         <f>IF(AND(S12="PARTIAL",R12=0),"n/d",IFERROR(R12/Y12,"n/d"))</f>
         <v/>
       </c>
-      <c r="AA12" s="42">
+      <c r="AA12" s="67">
         <f>IFERROR(X12/V12,"n/d")</f>
         <v/>
       </c>
-      <c r="AB12" s="43">
+      <c r="AB12" s="68">
         <f>IFERROR(V12/W12,IFERROR(V12/(V12-X12),"n/d"))</f>
         <v/>
       </c>
@@ -5211,7 +5946,7 @@
           <t>Liquid apogee engine (Lockheed Martin A2100A bus)</t>
         </is>
       </c>
-      <c r="F13" s="36" t="inlineStr">
+      <c r="F13" s="61" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
@@ -5221,7 +5956,7 @@
           <t>n/d</t>
         </is>
       </c>
-      <c r="H13" s="37">
+      <c r="H13" s="62">
         <f>IFERROR(F13*G13,"n/d")</f>
         <v/>
       </c>
@@ -5230,7 +5965,7 @@
           <t>Chemical RCS thrusters</t>
         </is>
       </c>
-      <c r="J13" s="36" t="inlineStr">
+      <c r="J13" s="61" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
@@ -5240,7 +5975,7 @@
           <t>n/d</t>
         </is>
       </c>
-      <c r="L13" s="37">
+      <c r="L13" s="62">
         <f>IFERROR(J13*K13,"n/d")</f>
         <v/>
       </c>
@@ -5249,21 +5984,21 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N13" s="36" t="n">
+      <c r="N13" s="61" t="n">
         <v>0</v>
       </c>
       <c r="O13" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="P13" s="37">
+      <c r="P13" s="62">
         <f>IFERROR(N13*O13,"n/d")</f>
         <v/>
       </c>
-      <c r="Q13" s="38">
+      <c r="Q13" s="63">
         <f>IFERROR(H13+L13+P13,"incomplete")</f>
         <v/>
       </c>
-      <c r="R13" s="38">
+      <c r="R13" s="63">
         <f>IF(A13="Boosters",SUM(H13,P13),SUM(H13,L13,P13))</f>
         <v/>
       </c>
@@ -5271,36 +6006,36 @@
         <f>IF(A13="Boosters",IF(AND(ISNUMBER(H13),ISNUMBER(P13)),"complete","PARTIAL"),IF(ISNUMBER(Q13),"complete","PARTIAL"))</f>
         <v/>
       </c>
-      <c r="T13" s="39" t="n">
+      <c r="T13" s="64" t="n">
         <v>5000</v>
       </c>
-      <c r="U13" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="40">
+      <c r="U13" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="65">
         <f>IFERROR(T13-U13,"n/d")</f>
         <v/>
       </c>
-      <c r="W13" s="39" t="n">
+      <c r="W13" s="64" t="n">
         <v>2925</v>
       </c>
-      <c r="X13" s="40">
+      <c r="X13" s="65">
         <f>IFERROR(V13-W13,"n/d")</f>
         <v/>
       </c>
-      <c r="Y13" s="40">
+      <c r="Y13" s="65">
         <f>IFERROR(V13*g0,"n/d")</f>
         <v/>
       </c>
-      <c r="Z13" s="41">
+      <c r="Z13" s="66">
         <f>IF(AND(S13="PARTIAL",R13=0),"n/d",IFERROR(R13/Y13,"n/d"))</f>
         <v/>
       </c>
-      <c r="AA13" s="42">
+      <c r="AA13" s="67">
         <f>IFERROR(X13/V13,"n/d")</f>
         <v/>
       </c>
-      <c r="AB13" s="43">
+      <c r="AB13" s="68">
         <f>IFERROR(V13/W13,IFERROR(V13/(V13-X13),"n/d"))</f>
         <v/>
       </c>
@@ -5421,13 +6156,13 @@
           <t>OMS-E (refurbished Shuttle OMS engine, gimballed = TVC)</t>
         </is>
       </c>
-      <c r="F14" s="36" t="n">
+      <c r="F14" s="61" t="n">
         <v>26700</v>
       </c>
       <c r="G14" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="H14" s="37">
+      <c r="H14" s="62">
         <f>IFERROR(F14*G14,"n/d")</f>
         <v/>
       </c>
@@ -5436,13 +6171,13 @@
           <t>216 N RCS thruster (ArianeGroup, ATV-derived), 6 clusters of 4</t>
         </is>
       </c>
-      <c r="J14" s="36" t="n">
+      <c r="J14" s="61" t="n">
         <v>216</v>
       </c>
       <c r="K14" s="35" t="n">
         <v>24</v>
       </c>
-      <c r="L14" s="37">
+      <c r="L14" s="62">
         <f>IFERROR(J14*K14,"n/d")</f>
         <v/>
       </c>
@@ -5451,21 +6186,21 @@
           <t>Auxiliary engine (Aerojet Rocketdyne R-4D-11, 164:1 nozzle)</t>
         </is>
       </c>
-      <c r="N14" s="36" t="n">
+      <c r="N14" s="61" t="n">
         <v>489</v>
       </c>
       <c r="O14" s="35" t="n">
         <v>8</v>
       </c>
-      <c r="P14" s="37">
+      <c r="P14" s="62">
         <f>IFERROR(N14*O14,"n/d")</f>
         <v/>
       </c>
-      <c r="Q14" s="38">
+      <c r="Q14" s="63">
         <f>IFERROR(H14+L14+P14,"incomplete")</f>
         <v/>
       </c>
-      <c r="R14" s="38">
+      <c r="R14" s="63">
         <f>IF(A14="Boosters",SUM(H14,P14),SUM(H14,L14,P14))</f>
         <v/>
       </c>
@@ -5473,33 +6208,33 @@
         <f>IF(A14="Boosters",IF(AND(ISNUMBER(H14),ISNUMBER(P14)),"complete","PARTIAL"),IF(ISNUMBER(Q14),"complete","PARTIAL"))</f>
         <v/>
       </c>
-      <c r="T14" s="39" t="n">
+      <c r="T14" s="64" t="n">
         <v>26536</v>
       </c>
-      <c r="U14" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="40">
+      <c r="U14" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="65">
         <f>IFERROR(T14-U14,"n/d")</f>
         <v/>
       </c>
-      <c r="W14" s="39" t="n"/>
-      <c r="X14" s="40" t="n">
+      <c r="W14" s="64" t="n"/>
+      <c r="X14" s="65" t="n">
         <v>8618</v>
       </c>
-      <c r="Y14" s="40">
+      <c r="Y14" s="65">
         <f>IFERROR(V14*g0,"n/d")</f>
         <v/>
       </c>
-      <c r="Z14" s="41">
+      <c r="Z14" s="66">
         <f>IF(AND(S14="PARTIAL",R14=0),"n/d",IFERROR(R14/Y14,"n/d"))</f>
         <v/>
       </c>
-      <c r="AA14" s="42">
+      <c r="AA14" s="67">
         <f>IFERROR(X14/V14,"n/d")</f>
         <v/>
       </c>
-      <c r="AB14" s="43">
+      <c r="AB14" s="68">
         <f>IFERROR(V14/W14,IFERROR(V14/(V14-X14),"n/d"))</f>
         <v/>
       </c>
@@ -5618,13 +6353,13 @@
           <t>SPS (Service Propulsion System, Aerojet AJ10-137, gimballed = TVC)</t>
         </is>
       </c>
-      <c r="F15" s="36" t="n">
+      <c r="F15" s="61" t="n">
         <v>91190</v>
       </c>
       <c r="G15" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="37">
+      <c r="H15" s="62">
         <f>IFERROR(F15*G15,"n/d")</f>
         <v/>
       </c>
@@ -5633,13 +6368,13 @@
           <t>SM RCS engine, 100 lbf, 4 quads x 4 engines</t>
         </is>
       </c>
-      <c r="J15" s="36" t="n">
+      <c r="J15" s="61" t="n">
         <v>445</v>
       </c>
       <c r="K15" s="35" t="n">
         <v>16</v>
       </c>
-      <c r="L15" s="37">
+      <c r="L15" s="62">
         <f>IFERROR(J15*K15,"n/d")</f>
         <v/>
       </c>
@@ -5648,21 +6383,21 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N15" s="36" t="n">
+      <c r="N15" s="61" t="n">
         <v>0</v>
       </c>
       <c r="O15" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="P15" s="37">
+      <c r="P15" s="62">
         <f>IFERROR(N15*O15,"n/d")</f>
         <v/>
       </c>
-      <c r="Q15" s="38">
+      <c r="Q15" s="63">
         <f>IFERROR(H15+L15+P15,"incomplete")</f>
         <v/>
       </c>
-      <c r="R15" s="38">
+      <c r="R15" s="63">
         <f>IF(A15="Boosters",SUM(H15,P15),SUM(H15,L15,P15))</f>
         <v/>
       </c>
@@ -5670,37 +6405,37 @@
         <f>IF(A15="Boosters",IF(AND(ISNUMBER(H15),ISNUMBER(P15)),"complete","PARTIAL"),IF(ISNUMBER(Q15),"complete","PARTIAL"))</f>
         <v/>
       </c>
-      <c r="T15" s="39" t="n">
+      <c r="T15" s="64" t="n">
         <v>30320</v>
       </c>
-      <c r="U15" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="40">
+      <c r="U15" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="65">
         <f>IFERROR(T15-U15,"n/d")</f>
         <v/>
       </c>
-      <c r="W15" s="39" t="inlineStr">
+      <c r="W15" s="64" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="X15" s="40" t="n">
+      <c r="X15" s="65" t="n">
         <v>18410</v>
       </c>
-      <c r="Y15" s="40">
+      <c r="Y15" s="65">
         <f>IFERROR(V15*g0,"n/d")</f>
         <v/>
       </c>
-      <c r="Z15" s="41">
+      <c r="Z15" s="66">
         <f>IF(AND(S15="PARTIAL",R15=0),"n/d",IFERROR(R15/Y15,"n/d"))</f>
         <v/>
       </c>
-      <c r="AA15" s="42">
+      <c r="AA15" s="67">
         <f>IFERROR(X15/V15,"n/d")</f>
         <v/>
       </c>
-      <c r="AB15" s="43">
+      <c r="AB15" s="68">
         <f>IFERROR(V15/W15,IFERROR(V15/(V15-X15),"n/d"))</f>
         <v/>
       </c>
@@ -5819,13 +6554,13 @@
           <t>DPS descent engine (throttleable, gimballed = TVC), max thrust</t>
         </is>
       </c>
-      <c r="F16" s="36" t="n">
+      <c r="F16" s="61" t="n">
         <v>46700</v>
       </c>
       <c r="G16" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="H16" s="37">
+      <c r="H16" s="62">
         <f>IFERROR(F16*G16,"n/d")</f>
         <v/>
       </c>
@@ -5834,13 +6569,13 @@
           <t>LM RCS thrust chamber assembly, 100 lbf, 4 quads x 4</t>
         </is>
       </c>
-      <c r="J16" s="36" t="n">
+      <c r="J16" s="61" t="n">
         <v>445</v>
       </c>
       <c r="K16" s="35" t="n">
         <v>16</v>
       </c>
-      <c r="L16" s="37">
+      <c r="L16" s="62">
         <f>IFERROR(J16*K16,"n/d")</f>
         <v/>
       </c>
@@ -5849,21 +6584,21 @@
           <t>APS ascent engine (fixed, ascent stage only)</t>
         </is>
       </c>
-      <c r="N16" s="36" t="n">
+      <c r="N16" s="61" t="n">
         <v>15500</v>
       </c>
       <c r="O16" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="P16" s="37">
+      <c r="P16" s="62">
         <f>IFERROR(N16*O16,"n/d")</f>
         <v/>
       </c>
-      <c r="Q16" s="38">
+      <c r="Q16" s="63">
         <f>IFERROR(H16+L16+P16,"incomplete")</f>
         <v/>
       </c>
-      <c r="R16" s="38">
+      <c r="R16" s="63">
         <f>IF(A16="Boosters",SUM(H16,P16),SUM(H16,L16,P16))</f>
         <v/>
       </c>
@@ -5871,35 +6606,35 @@
         <f>IF(A16="Boosters",IF(AND(ISNUMBER(H16),ISNUMBER(P16)),"complete","PARTIAL"),IF(ISNUMBER(Q16),"complete","PARTIAL"))</f>
         <v/>
       </c>
-      <c r="T16" s="39" t="n">
+      <c r="T16" s="64" t="n">
         <v>15103</v>
       </c>
-      <c r="U16" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="40">
+      <c r="U16" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="65">
         <f>IFERROR(T16-U16,"n/d")</f>
         <v/>
       </c>
-      <c r="W16" s="39" t="n">
+      <c r="W16" s="64" t="n">
         <v>4479</v>
       </c>
-      <c r="X16" s="40" t="n">
+      <c r="X16" s="65" t="n">
         <v>10624</v>
       </c>
-      <c r="Y16" s="40">
+      <c r="Y16" s="65">
         <f>IFERROR(V16*g0,"n/d")</f>
         <v/>
       </c>
-      <c r="Z16" s="41">
+      <c r="Z16" s="66">
         <f>IF(AND(S16="PARTIAL",R16=0),"n/d",IFERROR(R16/Y16,"n/d"))</f>
         <v/>
       </c>
-      <c r="AA16" s="42">
+      <c r="AA16" s="67">
         <f>IFERROR(X16/V16,"n/d")</f>
         <v/>
       </c>
-      <c r="AB16" s="43">
+      <c r="AB16" s="68">
         <f>IFERROR(V16/W16,IFERROR(V16/(V16-X16),"n/d"))</f>
         <v/>
       </c>
@@ -6018,13 +6753,13 @@
           <t>SuperDraco abort engine, ~15,000 lbf each</t>
         </is>
       </c>
-      <c r="F17" s="36" t="n">
+      <c r="F17" s="61" t="n">
         <v>66723</v>
       </c>
       <c r="G17" s="35" t="n">
         <v>8</v>
       </c>
-      <c r="H17" s="37">
+      <c r="H17" s="62">
         <f>IFERROR(F17*G17,"n/d")</f>
         <v/>
       </c>
@@ -6033,13 +6768,13 @@
           <t>Draco thruster, 90 lbf</t>
         </is>
       </c>
-      <c r="J17" s="36" t="n">
+      <c r="J17" s="61" t="n">
         <v>400</v>
       </c>
       <c r="K17" s="35" t="n">
         <v>16</v>
       </c>
-      <c r="L17" s="37">
+      <c r="L17" s="62">
         <f>IFERROR(J17*K17,"n/d")</f>
         <v/>
       </c>
@@ -6048,21 +6783,21 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N17" s="36" t="n">
+      <c r="N17" s="61" t="n">
         <v>0</v>
       </c>
       <c r="O17" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="P17" s="37">
+      <c r="P17" s="62">
         <f>IFERROR(N17*O17,"n/d")</f>
         <v/>
       </c>
-      <c r="Q17" s="38">
+      <c r="Q17" s="63">
         <f>IFERROR(H17+L17+P17,"incomplete")</f>
         <v/>
       </c>
-      <c r="R17" s="38">
+      <c r="R17" s="63">
         <f>IF(A17="Boosters",SUM(H17,P17),SUM(H17,L17,P17))</f>
         <v/>
       </c>
@@ -6070,40 +6805,40 @@
         <f>IF(A17="Boosters",IF(AND(ISNUMBER(H17),ISNUMBER(P17)),"complete","PARTIAL"),IF(ISNUMBER(Q17),"complete","PARTIAL"))</f>
         <v/>
       </c>
-      <c r="T17" s="39" t="inlineStr">
+      <c r="T17" s="64" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="U17" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="40">
+      <c r="U17" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="65">
         <f>IFERROR(T17-U17,"n/d")</f>
         <v/>
       </c>
-      <c r="W17" s="39" t="inlineStr">
+      <c r="W17" s="64" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="X17" s="40">
+      <c r="X17" s="65">
         <f>IFERROR(V17-W17,"n/d")</f>
         <v/>
       </c>
-      <c r="Y17" s="40">
+      <c r="Y17" s="65">
         <f>IFERROR(V17*g0,"n/d")</f>
         <v/>
       </c>
-      <c r="Z17" s="41">
+      <c r="Z17" s="66">
         <f>IF(AND(S17="PARTIAL",R17=0),"n/d",IFERROR(R17/Y17,"n/d"))</f>
         <v/>
       </c>
-      <c r="AA17" s="42">
+      <c r="AA17" s="67">
         <f>IFERROR(X17/V17,"n/d")</f>
         <v/>
       </c>
-      <c r="AB17" s="43">
+      <c r="AB17" s="68">
         <f>IFERROR(V17/W17,IFERROR(V17/(V17-X17),"n/d"))</f>
         <v/>
       </c>
@@ -6226,13 +6961,13 @@
           <t>Leros-1b bipropellant main engine (FIXED, no gimbal)</t>
         </is>
       </c>
-      <c r="F18" s="36" t="n">
+      <c r="F18" s="61" t="n">
         <v>645</v>
       </c>
       <c r="G18" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="H18" s="37">
+      <c r="H18" s="62">
         <f>IFERROR(F18*G18,"n/d")</f>
         <v/>
       </c>
@@ -6241,7 +6976,7 @@
           <t>Monopropellant hydrazine RCS thruster (4 rocket engine modules)</t>
         </is>
       </c>
-      <c r="J18" s="36" t="inlineStr">
+      <c r="J18" s="61" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
@@ -6249,7 +6984,7 @@
       <c r="K18" s="35" t="n">
         <v>12</v>
       </c>
-      <c r="L18" s="37">
+      <c r="L18" s="62">
         <f>IFERROR(J18*K18,"n/d")</f>
         <v/>
       </c>
@@ -6258,21 +6993,21 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N18" s="36" t="n">
+      <c r="N18" s="61" t="n">
         <v>0</v>
       </c>
       <c r="O18" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="P18" s="37">
+      <c r="P18" s="62">
         <f>IFERROR(N18*O18,"n/d")</f>
         <v/>
       </c>
-      <c r="Q18" s="38">
+      <c r="Q18" s="63">
         <f>IFERROR(H18+L18+P18,"incomplete")</f>
         <v/>
       </c>
-      <c r="R18" s="38">
+      <c r="R18" s="63">
         <f>IF(A18="Boosters",SUM(H18,P18),SUM(H18,L18,P18))</f>
         <v/>
       </c>
@@ -6280,35 +7015,35 @@
         <f>IF(A18="Boosters",IF(AND(ISNUMBER(H18),ISNUMBER(P18)),"complete","PARTIAL"),IF(ISNUMBER(Q18),"complete","PARTIAL"))</f>
         <v/>
       </c>
-      <c r="T18" s="39" t="n">
+      <c r="T18" s="64" t="n">
         <v>3625</v>
       </c>
-      <c r="U18" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="40">
+      <c r="U18" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="65">
         <f>IFERROR(T18-U18,"n/d")</f>
         <v/>
       </c>
-      <c r="W18" s="39" t="n">
+      <c r="W18" s="64" t="n">
         <v>1593</v>
       </c>
-      <c r="X18" s="40" t="n">
+      <c r="X18" s="65" t="n">
         <v>2032</v>
       </c>
-      <c r="Y18" s="40">
+      <c r="Y18" s="65">
         <f>IFERROR(V18*g0,"n/d")</f>
         <v/>
       </c>
-      <c r="Z18" s="41">
+      <c r="Z18" s="66">
         <f>IF(AND(S18="PARTIAL",R18=0),"n/d",IFERROR(R18/Y18,"n/d"))</f>
         <v/>
       </c>
-      <c r="AA18" s="42">
+      <c r="AA18" s="67">
         <f>IFERROR(X18/V18,"n/d")</f>
         <v/>
       </c>
-      <c r="AB18" s="43">
+      <c r="AB18" s="68">
         <f>IFERROR(V18/W18,IFERROR(V18/(V18-X18),"n/d"))</f>
         <v/>
       </c>
@@ -6429,13 +7164,13 @@
           <t>Main Engine A/B, 445 N gimballed (MEB a cold spare, never used)</t>
         </is>
       </c>
-      <c r="F19" s="36" t="n">
+      <c r="F19" s="61" t="n">
         <v>445</v>
       </c>
       <c r="G19" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="H19" s="37">
+      <c r="H19" s="62">
         <f>IFERROR(F19*G19,"n/d")</f>
         <v/>
       </c>
@@ -6444,13 +7179,13 @@
           <t>Monopropellant 1.0 N RCS thruster (2 branches x 8)</t>
         </is>
       </c>
-      <c r="J19" s="36" t="n">
+      <c r="J19" s="61" t="n">
         <v>1</v>
       </c>
       <c r="K19" s="35" t="n">
         <v>16</v>
       </c>
-      <c r="L19" s="37">
+      <c r="L19" s="62">
         <f>IFERROR(J19*K19,"n/d")</f>
         <v/>
       </c>
@@ -6459,21 +7194,21 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N19" s="36" t="n">
+      <c r="N19" s="61" t="n">
         <v>0</v>
       </c>
       <c r="O19" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="P19" s="37">
+      <c r="P19" s="62">
         <f>IFERROR(N19*O19,"n/d")</f>
         <v/>
       </c>
-      <c r="Q19" s="38">
+      <c r="Q19" s="63">
         <f>IFERROR(H19+L19+P19,"incomplete")</f>
         <v/>
       </c>
-      <c r="R19" s="38">
+      <c r="R19" s="63">
         <f>IF(A19="Boosters",SUM(H19,P19),SUM(H19,L19,P19))</f>
         <v/>
       </c>
@@ -6481,36 +7216,36 @@
         <f>IF(A19="Boosters",IF(AND(ISNUMBER(H19),ISNUMBER(P19)),"complete","PARTIAL"),IF(ISNUMBER(Q19),"complete","PARTIAL"))</f>
         <v/>
       </c>
-      <c r="T19" s="39" t="n">
+      <c r="T19" s="64" t="n">
         <v>5574</v>
       </c>
-      <c r="U19" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="40">
+      <c r="U19" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="65">
         <f>IFERROR(T19-U19,"n/d")</f>
         <v/>
       </c>
-      <c r="W19" s="39" t="n">
+      <c r="W19" s="64" t="n">
         <v>2523</v>
       </c>
-      <c r="X19" s="40">
+      <c r="X19" s="65">
         <f>IFERROR(V19-W19,"n/d")</f>
         <v/>
       </c>
-      <c r="Y19" s="40">
+      <c r="Y19" s="65">
         <f>IFERROR(V19*g0,"n/d")</f>
         <v/>
       </c>
-      <c r="Z19" s="41">
+      <c r="Z19" s="66">
         <f>IF(AND(S19="PARTIAL",R19=0),"n/d",IFERROR(R19/Y19,"n/d"))</f>
         <v/>
       </c>
-      <c r="AA19" s="42">
+      <c r="AA19" s="67">
         <f>IFERROR(X19/V19,"n/d")</f>
         <v/>
       </c>
-      <c r="AB19" s="43">
+      <c r="AB19" s="68">
         <f>IFERROR(V19/W19,IFERROR(V19/(V19-X19),"n/d"))</f>
         <v/>
       </c>
@@ -6631,13 +7366,13 @@
           <t>4.4 N hydrazine thruster (course correction)</t>
         </is>
       </c>
-      <c r="F20" s="36" t="n">
+      <c r="F20" s="61" t="n">
         <v>4.4</v>
       </c>
       <c r="G20" s="35" t="n">
         <v>4</v>
       </c>
-      <c r="H20" s="37">
+      <c r="H20" s="62">
         <f>IFERROR(F20*G20,"n/d")</f>
         <v/>
       </c>
@@ -6646,13 +7381,13 @@
           <t>0.8 N hydrazine thruster (pointing, spin up/down)</t>
         </is>
       </c>
-      <c r="J20" s="36" t="n">
+      <c r="J20" s="61" t="n">
         <v>0.8</v>
       </c>
       <c r="K20" s="35" t="n">
         <v>12</v>
       </c>
-      <c r="L20" s="37">
+      <c r="L20" s="62">
         <f>IFERROR(J20*K20,"n/d")</f>
         <v/>
       </c>
@@ -6661,21 +7396,21 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N20" s="36" t="n">
+      <c r="N20" s="61" t="n">
         <v>0</v>
       </c>
       <c r="O20" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="P20" s="37">
+      <c r="P20" s="62">
         <f>IFERROR(N20*O20,"n/d")</f>
         <v/>
       </c>
-      <c r="Q20" s="38">
+      <c r="Q20" s="63">
         <f>IFERROR(H20+L20+P20,"incomplete")</f>
         <v/>
       </c>
-      <c r="R20" s="38">
+      <c r="R20" s="63">
         <f>IF(A20="Boosters",SUM(H20,P20),SUM(H20,L20,P20))</f>
         <v/>
       </c>
@@ -6683,33 +7418,33 @@
         <f>IF(A20="Boosters",IF(AND(ISNUMBER(H20),ISNUMBER(P20)),"complete","PARTIAL"),IF(ISNUMBER(Q20),"complete","PARTIAL"))</f>
         <v/>
       </c>
-      <c r="T20" s="39" t="n">
+      <c r="T20" s="64" t="n">
         <v>478</v>
       </c>
-      <c r="U20" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="40">
+      <c r="U20" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="65">
         <f>IFERROR(T20-U20,"n/d")</f>
         <v/>
       </c>
-      <c r="W20" s="39" t="n"/>
-      <c r="X20" s="40" t="n">
+      <c r="W20" s="64" t="n"/>
+      <c r="X20" s="65" t="n">
         <v>77</v>
       </c>
-      <c r="Y20" s="40">
+      <c r="Y20" s="65">
         <f>IFERROR(V20*g0,"n/d")</f>
         <v/>
       </c>
-      <c r="Z20" s="41">
+      <c r="Z20" s="66">
         <f>IF(AND(S20="PARTIAL",R20=0),"n/d",IFERROR(R20/Y20,"n/d"))</f>
         <v/>
       </c>
-      <c r="AA20" s="42">
+      <c r="AA20" s="67">
         <f>IFERROR(X20/V20,"n/d")</f>
         <v/>
       </c>
-      <c r="AB20" s="43">
+      <c r="AB20" s="68">
         <f>IFERROR(V20/W20,IFERROR(V20/(V20-X20),"n/d"))</f>
         <v/>
       </c>
@@ -6830,13 +7565,13 @@
           <t>27.5 N engine (24 installed; max 8 fired simultaneously)</t>
         </is>
       </c>
-      <c r="F21" s="36" t="n">
+      <c r="F21" s="61" t="n">
         <v>27.5</v>
       </c>
       <c r="G21" s="35" t="n">
         <v>24</v>
       </c>
-      <c r="H21" s="37">
+      <c r="H21" s="62">
         <f>IFERROR(F21*G21,"n/d")</f>
         <v/>
       </c>
@@ -6845,13 +7580,13 @@
           <t>Same engine set - no separate RCS tier</t>
         </is>
       </c>
-      <c r="J21" s="36" t="n">
+      <c r="J21" s="61" t="n">
         <v>0</v>
       </c>
       <c r="K21" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="37">
+      <c r="L21" s="62">
         <f>IFERROR(J21*K21,"n/d")</f>
         <v/>
       </c>
@@ -6860,21 +7595,21 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N21" s="36" t="n">
+      <c r="N21" s="61" t="n">
         <v>0</v>
       </c>
       <c r="O21" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="P21" s="37">
+      <c r="P21" s="62">
         <f>IFERROR(N21*O21,"n/d")</f>
         <v/>
       </c>
-      <c r="Q21" s="38">
+      <c r="Q21" s="63">
         <f>IFERROR(H21+L21+P21,"incomplete")</f>
         <v/>
       </c>
-      <c r="R21" s="38">
+      <c r="R21" s="63">
         <f>IF(A21="Boosters",SUM(H21,P21),SUM(H21,L21,P21))</f>
         <v/>
       </c>
@@ -6882,33 +7617,33 @@
         <f>IF(A21="Boosters",IF(AND(ISNUMBER(H21),ISNUMBER(P21)),"complete","PARTIAL"),IF(ISNUMBER(Q21),"complete","PARTIAL"))</f>
         <v/>
       </c>
-      <c r="T21" s="39" t="n">
+      <c r="T21" s="64" t="n">
         <v>5800</v>
       </c>
-      <c r="U21" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="40">
+      <c r="U21" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="65">
         <f>IFERROR(T21-U21,"n/d")</f>
         <v/>
       </c>
-      <c r="W21" s="39" t="n"/>
-      <c r="X21" s="40" t="n">
+      <c r="W21" s="64" t="n"/>
+      <c r="X21" s="65" t="n">
         <v>2750</v>
       </c>
-      <c r="Y21" s="40">
+      <c r="Y21" s="65">
         <f>IFERROR(V21*g0,"n/d")</f>
         <v/>
       </c>
-      <c r="Z21" s="41">
+      <c r="Z21" s="66">
         <f>IF(AND(S21="PARTIAL",R21=0),"n/d",IFERROR(R21/Y21,"n/d"))</f>
         <v/>
       </c>
-      <c r="AA21" s="42">
+      <c r="AA21" s="67">
         <f>IFERROR(X21/V21,"n/d")</f>
         <v/>
       </c>
-      <c r="AB21" s="43">
+      <c r="AB21" s="68">
         <f>IFERROR(V21/W21,IFERROR(V21/(V21-X21),"n/d"))</f>
         <v/>
       </c>
@@ -7031,13 +7766,13 @@
           <t>None - no main engine (propulsion module jettisoned after launch)</t>
         </is>
       </c>
-      <c r="F22" s="36" t="n">
+      <c r="F22" s="61" t="n">
         <v>0</v>
       </c>
       <c r="G22" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="37">
+      <c r="H22" s="62">
         <f>IFERROR(F22*G22,"n/d")</f>
         <v/>
       </c>
@@ -7046,13 +7781,13 @@
           <t>Hydrazine thruster (12 attitude control + 4 TCM)</t>
         </is>
       </c>
-      <c r="J22" s="36" t="n">
+      <c r="J22" s="61" t="n">
         <v>0.85</v>
       </c>
       <c r="K22" s="35" t="n">
         <v>16</v>
       </c>
-      <c r="L22" s="37">
+      <c r="L22" s="62">
         <f>IFERROR(J22*K22,"n/d")</f>
         <v/>
       </c>
@@ -7061,21 +7796,21 @@
           <t>None</t>
         </is>
       </c>
-      <c r="N22" s="36" t="n">
+      <c r="N22" s="61" t="n">
         <v>0</v>
       </c>
       <c r="O22" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="P22" s="37">
+      <c r="P22" s="62">
         <f>IFERROR(N22*O22,"n/d")</f>
         <v/>
       </c>
-      <c r="Q22" s="38">
+      <c r="Q22" s="63">
         <f>IFERROR(H22+L22+P22,"incomplete")</f>
         <v/>
       </c>
-      <c r="R22" s="38">
+      <c r="R22" s="63">
         <f>IF(A22="Boosters",SUM(H22,P22),SUM(H22,L22,P22))</f>
         <v/>
       </c>
@@ -7083,38 +7818,38 @@
         <f>IF(A22="Boosters",IF(AND(ISNUMBER(H22),ISNUMBER(P22)),"complete","PARTIAL"),IF(ISNUMBER(Q22),"complete","PARTIAL"))</f>
         <v/>
       </c>
-      <c r="T22" s="39" t="n">
+      <c r="T22" s="64" t="n">
         <v>815</v>
       </c>
-      <c r="U22" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="40">
+      <c r="U22" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="65">
         <f>IFERROR(T22-U22,"n/d")</f>
         <v/>
       </c>
-      <c r="W22" s="39" t="inlineStr">
+      <c r="W22" s="64" t="inlineStr">
         <is>
           <t>n/d</t>
         </is>
       </c>
-      <c r="X22" s="40">
+      <c r="X22" s="65">
         <f>IFERROR(V22-W22,"n/d")</f>
         <v/>
       </c>
-      <c r="Y22" s="40">
+      <c r="Y22" s="65">
         <f>IFERROR(V22*g0,"n/d")</f>
         <v/>
       </c>
-      <c r="Z22" s="41">
+      <c r="Z22" s="66">
         <f>IF(AND(S22="PARTIAL",R22=0),"n/d",IFERROR(R22/Y22,"n/d"))</f>
         <v/>
       </c>
-      <c r="AA22" s="42">
+      <c r="AA22" s="67">
         <f>IFERROR(X22/V22,"n/d")</f>
         <v/>
       </c>
-      <c r="AB22" s="43">
+      <c r="AB22" s="68">
         <f>IFERROR(V22/W22,IFERROR(V22/(V22-X22),"n/d"))</f>
         <v/>
       </c>
